--- a/data/trans_orig/IP18E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP18E-Habitat-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106557</t>
+          <t>106433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113377</t>
+          <t>113395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113866</t>
+          <t>113703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123270</t>
+          <t>123098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223274</t>
+          <t>224070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>235037</t>
+          <t>234635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146140</t>
+          <t>145827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155505</t>
+          <t>155377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>159625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170106</t>
+          <t>170010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>309495</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>322519</t>
+          <t>322818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105529</t>
+          <t>105341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115068</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115203</t>
+          <t>115423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125303</t>
+          <t>125240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223997</t>
+          <t>223650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238120</t>
+          <t>237402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>21668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9306</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172400</t>
+          <t>170825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183596</t>
+          <t>183161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157876</t>
+          <t>157842</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169725</t>
+          <t>169368</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333944</t>
+          <t>333096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>349738</t>
+          <t>350533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>13774</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>51125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30864</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>50911</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>559770</t>
+          <t>559408</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>579694</t>
+          <t>579792</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1106523</t>
+          <t>1106063</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1134395</t>
+          <t>1134911</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116492</t>
+          <t>115573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126384</t>
+          <t>126143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140151</t>
+          <t>140375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145630</t>
+          <t>145632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260187</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271073</t>
+          <t>271134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184654</t>
+          <t>184640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191306</t>
+          <t>191301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187169</t>
+          <t>187430</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>199033</t>
+          <t>198934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375401</t>
+          <t>375462</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>388515</t>
+          <t>389425</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127076</t>
+          <t>127191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137011</t>
+          <t>136905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139001</t>
+          <t>138534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149085</t>
+          <t>149472</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269765</t>
+          <t>269757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283893</t>
+          <t>283884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27362</t>
+          <t>27748</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>179420</t>
+          <t>180824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191959</t>
+          <t>192521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183445</t>
+          <t>183431</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>194752</t>
+          <t>194891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>368414</t>
+          <t>367497</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>384146</t>
+          <t>384280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20212</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34866</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>29350</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58590</t>
+          <t>57344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>662339</t>
+          <t>661538</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>682374</t>
+          <t>682051</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1290435</t>
+          <t>1291657</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1318748</t>
+          <t>1317988</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>109029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118586</t>
+          <t>118264</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122090</t>
+          <t>122895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130364</t>
+          <t>130330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>234731</t>
+          <t>235129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>247145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20426</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>177523</t>
+          <t>177545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>186991</t>
+          <t>187555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194369</t>
+          <t>194084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203307</t>
+          <t>203751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374329</t>
+          <t>374344</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>388293</t>
+          <t>388564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125135</t>
+          <t>125771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133620</t>
+          <t>133605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135050</t>
+          <t>134498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142720</t>
+          <t>142767</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263063</t>
+          <t>262622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274209</t>
+          <t>274098</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,47 +8757,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>9031</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>4440</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1609</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>9534</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>16975</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18741</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173577</t>
+          <t>174276</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155779</t>
+          <t>156381</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169043</t>
+          <t>168758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>334084</t>
+          <t>334900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351794</t>
+          <t>351546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>38130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71207</t>
+          <t>71711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34337</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38217</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>28014</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>44108</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49155</t>
+          <t>49163</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>69520</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>38776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>52923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19003</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21844</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>44453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52157</t>
+          <t>52329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21697</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
